--- a/data/cc_inventory_sectors.xlsx
+++ b/data/cc_inventory_sectors.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="summaries" sheetId="2" r:id="rId1"/>
     <sheet name="full" sheetId="1" r:id="rId2"/>
+    <sheet name="saved" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="420">
   <si>
     <t>sector</t>
   </si>
@@ -2833,45 +2834,41 @@
   <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="75.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="75.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="62.7109375" customWidth="1"/>
-    <col min="5" max="5" width="38.7109375" customWidth="1"/>
-    <col min="6" max="6" width="46.7109375" customWidth="1"/>
-    <col min="7" max="7" width="62.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
+    <col min="6" max="6" width="62.7109375" customWidth="1"/>
+    <col min="7" max="7" width="54.7109375" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" t="s">
         <v>387</v>
       </c>
@@ -2880,69 +2877,42 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2">
         <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
       <c r="C3">
         <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
       <c r="C4">
         <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -2956,31 +2926,28 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
       <c r="H5" t="b">
         <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
       </c>
       <c r="J5" t="s">
         <v>391</v>
@@ -2991,31 +2958,28 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
       <c r="H6" t="b">
         <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
       </c>
       <c r="J6" t="s">
         <v>391</v>
@@ -3026,31 +2990,28 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
       <c r="H7" t="b">
         <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
       </c>
       <c r="J7" t="s">
         <v>391</v>
@@ -3060,26 +3021,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
       <c r="C8">
         <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -3093,31 +3042,28 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
       <c r="H9" t="b">
         <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
       </c>
       <c r="J9" t="s">
         <v>392</v>
@@ -3128,31 +3074,28 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
       <c r="H10" t="b">
         <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>35</v>
       </c>
       <c r="J10" t="s">
         <v>392</v>
@@ -3163,31 +3106,28 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
       <c r="H11" t="b">
         <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>38</v>
       </c>
       <c r="J11" t="s">
         <v>392</v>
@@ -3198,31 +3138,28 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
       <c r="H12" t="b">
         <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>41</v>
       </c>
       <c r="J12" t="s">
         <v>392</v>
@@ -3233,31 +3170,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
       <c r="H13" t="b">
         <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>44</v>
       </c>
       <c r="J13" t="s">
         <v>392</v>
@@ -3268,31 +3202,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
         <v>47</v>
       </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
       <c r="H14" t="b">
         <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
       </c>
       <c r="J14" t="s">
         <v>392</v>
@@ -3303,31 +3234,28 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
       <c r="H15" t="b">
         <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>50</v>
       </c>
       <c r="J15" t="s">
         <v>392</v>
@@ -3337,26 +3265,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
       <c r="C16">
         <v>3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>53</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -3370,31 +3286,28 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
         <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>55</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
         <v>56</v>
       </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>53</v>
-      </c>
       <c r="H17" t="b">
         <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>56</v>
       </c>
       <c r="J17" t="s">
         <v>393</v>
@@ -3405,31 +3318,28 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
       <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
       <c r="H18" t="b">
         <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>59</v>
       </c>
       <c r="J18" t="s">
         <v>393</v>
@@ -3440,31 +3350,28 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
         <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
         <v>62</v>
       </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>53</v>
-      </c>
       <c r="H19" t="b">
         <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>62</v>
       </c>
       <c r="J19" t="s">
         <v>393</v>
@@ -3475,31 +3382,28 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
         <v>65</v>
       </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
       <c r="H20" t="b">
         <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>65</v>
       </c>
       <c r="J20" t="s">
         <v>393</v>
@@ -3510,31 +3414,28 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
         <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
       </c>
       <c r="C21">
         <v>4</v>
       </c>
       <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>53</v>
-      </c>
       <c r="H21" t="b">
         <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>68</v>
       </c>
       <c r="J21" t="s">
         <v>393</v>
@@ -3544,26 +3445,14 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
       <c r="C22">
         <v>3</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>71</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -3577,31 +3466,28 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
         <v>72</v>
-      </c>
-      <c r="B23" t="s">
-        <v>73</v>
       </c>
       <c r="C23">
         <v>4</v>
       </c>
       <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>71</v>
-      </c>
       <c r="H23" t="b">
         <v>1</v>
-      </c>
-      <c r="I23" t="s">
-        <v>74</v>
       </c>
       <c r="J23" t="s">
         <v>394</v>
@@ -3612,31 +3498,28 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>75</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
       </c>
       <c r="C24">
         <v>4</v>
       </c>
       <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" t="s">
         <v>77</v>
       </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>71</v>
-      </c>
       <c r="H24" t="b">
         <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>77</v>
       </c>
       <c r="J24" t="s">
         <v>394</v>
@@ -3647,31 +3530,28 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
         <v>78</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>71</v>
-      </c>
       <c r="H25" t="b">
         <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>80</v>
       </c>
       <c r="J25" t="s">
         <v>394</v>
@@ -3682,22 +3562,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
         <v>81</v>
       </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
         <v>50</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
       </c>
       <c r="G26" t="s">
         <v>50</v>
@@ -3705,9 +3585,6 @@
       <c r="H26" t="b">
         <v>1</v>
       </c>
-      <c r="I26" t="s">
-        <v>50</v>
-      </c>
       <c r="J26" t="s">
         <v>394</v>
       </c>
@@ -3716,23 +3593,14 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
       <c r="C27">
         <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>85</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -3745,26 +3613,14 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
       <c r="C28">
         <v>3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G28" t="s">
-        <v>88</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -3778,31 +3634,28 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
         <v>89</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
       </c>
       <c r="C29">
         <v>4</v>
       </c>
       <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" t="s">
         <v>91</v>
       </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" t="s">
-        <v>88</v>
-      </c>
       <c r="H29" t="b">
         <v>1</v>
-      </c>
-      <c r="I29" t="s">
-        <v>91</v>
       </c>
       <c r="J29" t="s">
         <v>395</v>
@@ -3813,31 +3666,28 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
         <v>92</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
       </c>
       <c r="C30">
         <v>4</v>
       </c>
       <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s">
         <v>94</v>
       </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" t="s">
-        <v>88</v>
-      </c>
       <c r="H30" t="b">
         <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>94</v>
       </c>
       <c r="J30" t="s">
         <v>395</v>
@@ -3848,31 +3698,28 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
         <v>95</v>
-      </c>
-      <c r="B31" t="s">
-        <v>96</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s">
         <v>50</v>
       </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G31" t="s">
-        <v>88</v>
-      </c>
       <c r="H31" t="b">
         <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>50</v>
       </c>
       <c r="J31" t="s">
         <v>395</v>
@@ -3882,26 +3729,14 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
       <c r="C32">
         <v>3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" t="s">
-        <v>99</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -3915,31 +3750,28 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
         <v>100</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
       </c>
       <c r="C33">
         <v>4</v>
       </c>
       <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" t="s">
         <v>102</v>
       </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" t="s">
-        <v>99</v>
-      </c>
       <c r="H33" t="b">
         <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>102</v>
       </c>
       <c r="J33" t="s">
         <v>395</v>
@@ -3950,31 +3782,28 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
       <c r="C34">
         <v>4</v>
       </c>
       <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" t="s">
         <v>105</v>
       </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" t="s">
-        <v>99</v>
-      </c>
       <c r="H34" t="b">
         <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>105</v>
       </c>
       <c r="J34" t="s">
         <v>395</v>
@@ -3985,31 +3814,28 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
         <v>106</v>
-      </c>
-      <c r="B35" t="s">
-        <v>107</v>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" t="s">
         <v>108</v>
       </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>85</v>
-      </c>
-      <c r="G35" t="s">
-        <v>99</v>
-      </c>
       <c r="H35" t="b">
         <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>108</v>
       </c>
       <c r="J35" t="s">
         <v>395</v>
@@ -4020,31 +3846,28 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
         <v>109</v>
-      </c>
-      <c r="B36" t="s">
-        <v>110</v>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
       <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" t="s">
         <v>50</v>
       </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G36" t="s">
-        <v>99</v>
-      </c>
       <c r="H36" t="b">
         <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>50</v>
       </c>
       <c r="J36" t="s">
         <v>395</v>
@@ -4054,23 +3877,14 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B37" t="s">
-        <v>112</v>
-      </c>
       <c r="C37">
         <v>2</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>113</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -4084,22 +3898,22 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
         <v>114</v>
       </c>
-      <c r="B38" t="s">
-        <v>115</v>
-      </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" t="s">
         <v>116</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>113</v>
       </c>
       <c r="G38" t="s">
         <v>116</v>
@@ -4107,9 +3921,6 @@
       <c r="H38" t="b">
         <v>1</v>
       </c>
-      <c r="I38" t="s">
-        <v>116</v>
-      </c>
       <c r="J38" t="s">
         <v>395</v>
       </c>
@@ -4119,22 +3930,22 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" t="s">
         <v>117</v>
       </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" t="s">
         <v>119</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
-        <v>113</v>
       </c>
       <c r="G39" t="s">
         <v>119</v>
@@ -4142,9 +3953,6 @@
       <c r="H39" t="b">
         <v>1</v>
       </c>
-      <c r="I39" t="s">
-        <v>119</v>
-      </c>
       <c r="J39" t="s">
         <v>395</v>
       </c>
@@ -4154,22 +3962,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
         <v>120</v>
       </c>
-      <c r="B40" t="s">
-        <v>121</v>
-      </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" t="s">
         <v>50</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>113</v>
       </c>
       <c r="G40" t="s">
         <v>50</v>
@@ -4177,9 +3985,6 @@
       <c r="H40" t="b">
         <v>1</v>
       </c>
-      <c r="I40" t="s">
-        <v>50</v>
-      </c>
       <c r="J40" t="s">
         <v>395</v>
       </c>
@@ -4188,49 +3993,28 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B41" t="s">
-        <v>123</v>
-      </c>
       <c r="C41">
         <v>2</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" t="s">
-        <v>124</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B42" t="s">
-        <v>126</v>
-      </c>
       <c r="C42">
         <v>3</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>124</v>
-      </c>
-      <c r="G42" t="s">
-        <v>127</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -4238,80 +4022,74 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" t="s">
         <v>128</v>
-      </c>
-      <c r="B43" t="s">
-        <v>129</v>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" t="s">
         <v>130</v>
       </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>124</v>
-      </c>
-      <c r="G43" t="s">
-        <v>127</v>
-      </c>
       <c r="H43" t="b">
         <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" t="s">
         <v>131</v>
-      </c>
-      <c r="B44" t="s">
-        <v>132</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" t="s">
         <v>133</v>
       </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" t="s">
-        <v>124</v>
-      </c>
-      <c r="G44" t="s">
-        <v>127</v>
-      </c>
       <c r="H44" t="b">
         <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" t="s">
         <v>134</v>
       </c>
-      <c r="B45" t="s">
-        <v>135</v>
-      </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
         <v>136</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>124</v>
       </c>
       <c r="G45" t="s">
         <v>136</v>
@@ -4319,28 +4097,25 @@
       <c r="H45" t="b">
         <v>1</v>
       </c>
-      <c r="I45" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" t="s">
         <v>137</v>
       </c>
-      <c r="B46" t="s">
-        <v>138</v>
-      </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" t="s">
         <v>139</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>124</v>
       </c>
       <c r="G46" t="s">
         <v>139</v>
@@ -4348,31 +4123,16 @@
       <c r="H46" t="b">
         <v>1</v>
       </c>
-      <c r="I46" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B47" t="s">
-        <v>141</v>
-      </c>
       <c r="C47">
         <v>3</v>
-      </c>
-      <c r="D47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" t="s">
-        <v>124</v>
-      </c>
-      <c r="G47" t="s">
-        <v>142</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -4380,100 +4140,79 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
         <v>143</v>
-      </c>
-      <c r="B48" t="s">
-        <v>144</v>
       </c>
       <c r="C48">
         <v>4</v>
       </c>
       <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" t="s">
         <v>145</v>
       </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>124</v>
-      </c>
-      <c r="G48" t="s">
-        <v>142</v>
-      </c>
       <c r="H48" t="b">
         <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" t="s">
         <v>146</v>
-      </c>
-      <c r="B49" t="s">
-        <v>147</v>
       </c>
       <c r="C49">
         <v>4</v>
       </c>
       <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
+        <v>142</v>
+      </c>
+      <c r="G49" t="s">
         <v>148</v>
       </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>124</v>
-      </c>
-      <c r="G49" t="s">
-        <v>142</v>
-      </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
-      <c r="I49" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B50" t="s">
-        <v>150</v>
-      </c>
       <c r="C50">
         <v>1</v>
-      </c>
-      <c r="D50" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" t="s">
-        <v>151</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B51" t="s">
-        <v>153</v>
-      </c>
       <c r="C51">
         <v>2</v>
-      </c>
-      <c r="D51" t="s">
-        <v>154</v>
-      </c>
-      <c r="E51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F51" t="s">
-        <v>154</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
@@ -4487,22 +4226,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
         <v>155</v>
       </c>
-      <c r="B52" t="s">
-        <v>156</v>
-      </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" t="s">
         <v>157</v>
-      </c>
-      <c r="E52" t="s">
-        <v>151</v>
-      </c>
-      <c r="F52" t="s">
-        <v>154</v>
       </c>
       <c r="G52" t="s">
         <v>157</v>
@@ -4510,9 +4249,6 @@
       <c r="H52" t="b">
         <v>1</v>
       </c>
-      <c r="I52" t="s">
-        <v>157</v>
-      </c>
       <c r="J52" t="s">
         <v>388</v>
       </c>
@@ -4522,22 +4258,22 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" t="s">
         <v>158</v>
       </c>
-      <c r="B53" t="s">
-        <v>159</v>
-      </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E53" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" t="s">
         <v>160</v>
-      </c>
-      <c r="E53" t="s">
-        <v>151</v>
-      </c>
-      <c r="F53" t="s">
-        <v>154</v>
       </c>
       <c r="G53" t="s">
         <v>160</v>
@@ -4545,9 +4281,6 @@
       <c r="H53" t="b">
         <v>1</v>
       </c>
-      <c r="I53" t="s">
-        <v>160</v>
-      </c>
       <c r="J53" t="s">
         <v>388</v>
       </c>
@@ -4557,22 +4290,22 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
         <v>161</v>
       </c>
-      <c r="B54" t="s">
-        <v>162</v>
-      </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
+        <v>151</v>
+      </c>
+      <c r="E54" t="s">
+        <v>154</v>
+      </c>
+      <c r="F54" t="s">
         <v>163</v>
-      </c>
-      <c r="E54" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" t="s">
-        <v>154</v>
       </c>
       <c r="G54" t="s">
         <v>163</v>
@@ -4580,9 +4313,6 @@
       <c r="H54" t="b">
         <v>1</v>
       </c>
-      <c r="I54" t="s">
-        <v>163</v>
-      </c>
       <c r="J54" t="s">
         <v>388</v>
       </c>
@@ -4592,22 +4322,22 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" t="s">
         <v>164</v>
       </c>
-      <c r="B55" t="s">
-        <v>165</v>
-      </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" t="s">
+        <v>154</v>
+      </c>
+      <c r="F55" t="s">
         <v>166</v>
-      </c>
-      <c r="E55" t="s">
-        <v>151</v>
-      </c>
-      <c r="F55" t="s">
-        <v>154</v>
       </c>
       <c r="G55" t="s">
         <v>166</v>
@@ -4615,9 +4345,6 @@
       <c r="H55" t="b">
         <v>1</v>
       </c>
-      <c r="I55" t="s">
-        <v>166</v>
-      </c>
       <c r="J55" t="s">
         <v>388</v>
       </c>
@@ -4626,23 +4353,14 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B56" t="s">
-        <v>168</v>
-      </c>
       <c r="C56">
         <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>169</v>
-      </c>
-      <c r="E56" t="s">
-        <v>151</v>
-      </c>
-      <c r="F56" t="s">
-        <v>169</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
@@ -4656,22 +4374,22 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s">
         <v>170</v>
       </c>
-      <c r="B57" t="s">
-        <v>171</v>
-      </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>169</v>
+      </c>
+      <c r="F57" t="s">
         <v>172</v>
-      </c>
-      <c r="E57" t="s">
-        <v>151</v>
-      </c>
-      <c r="F57" t="s">
-        <v>169</v>
       </c>
       <c r="G57" t="s">
         <v>172</v>
@@ -4679,9 +4397,6 @@
       <c r="H57" t="b">
         <v>1</v>
       </c>
-      <c r="I57" t="s">
-        <v>172</v>
-      </c>
       <c r="J57" t="s">
         <v>388</v>
       </c>
@@ -4691,22 +4406,22 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
         <v>173</v>
       </c>
-      <c r="B58" t="s">
-        <v>174</v>
-      </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" t="s">
+        <v>169</v>
+      </c>
+      <c r="F58" t="s">
         <v>50</v>
-      </c>
-      <c r="E58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F58" t="s">
-        <v>169</v>
       </c>
       <c r="G58" t="s">
         <v>50</v>
@@ -4714,9 +4429,6 @@
       <c r="H58" t="b">
         <v>1</v>
       </c>
-      <c r="I58" t="s">
-        <v>50</v>
-      </c>
       <c r="J58" t="s">
         <v>388</v>
       </c>
@@ -4726,22 +4438,22 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
         <v>175</v>
       </c>
-      <c r="B59" t="s">
-        <v>176</v>
-      </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" t="s">
+        <v>169</v>
+      </c>
+      <c r="F59" t="s">
         <v>177</v>
-      </c>
-      <c r="E59" t="s">
-        <v>151</v>
-      </c>
-      <c r="F59" t="s">
-        <v>169</v>
       </c>
       <c r="G59" t="s">
         <v>177</v>
@@ -4749,9 +4461,6 @@
       <c r="H59" t="b">
         <v>1</v>
       </c>
-      <c r="I59" t="s">
-        <v>177</v>
-      </c>
       <c r="J59" t="s">
         <v>388</v>
       </c>
@@ -4761,22 +4470,22 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
         <v>178</v>
       </c>
-      <c r="B60" t="s">
-        <v>179</v>
-      </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" t="s">
+        <v>169</v>
+      </c>
+      <c r="F60" t="s">
         <v>180</v>
-      </c>
-      <c r="E60" t="s">
-        <v>151</v>
-      </c>
-      <c r="F60" t="s">
-        <v>169</v>
       </c>
       <c r="G60" t="s">
         <v>180</v>
@@ -4784,9 +4493,6 @@
       <c r="H60" t="b">
         <v>1</v>
       </c>
-      <c r="I60" t="s">
-        <v>180</v>
-      </c>
       <c r="J60" t="s">
         <v>388</v>
       </c>
@@ -4796,22 +4502,22 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s">
         <v>181</v>
       </c>
-      <c r="B61" t="s">
-        <v>182</v>
-      </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
+        <v>151</v>
+      </c>
+      <c r="E61" t="s">
+        <v>169</v>
+      </c>
+      <c r="F61" t="s">
         <v>183</v>
-      </c>
-      <c r="E61" t="s">
-        <v>151</v>
-      </c>
-      <c r="F61" t="s">
-        <v>169</v>
       </c>
       <c r="G61" t="s">
         <v>183</v>
@@ -4819,9 +4525,6 @@
       <c r="H61" t="b">
         <v>1</v>
       </c>
-      <c r="I61" t="s">
-        <v>183</v>
-      </c>
       <c r="J61" t="s">
         <v>388</v>
       </c>
@@ -4831,22 +4534,22 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s">
         <v>184</v>
       </c>
-      <c r="B62" t="s">
-        <v>185</v>
-      </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E62" t="s">
+        <v>169</v>
+      </c>
+      <c r="F62" t="s">
         <v>186</v>
-      </c>
-      <c r="E62" t="s">
-        <v>151</v>
-      </c>
-      <c r="F62" t="s">
-        <v>169</v>
       </c>
       <c r="G62" t="s">
         <v>186</v>
@@ -4854,9 +4557,6 @@
       <c r="H62" t="b">
         <v>1</v>
       </c>
-      <c r="I62" t="s">
-        <v>186</v>
-      </c>
       <c r="J62" t="s">
         <v>388</v>
       </c>
@@ -4866,22 +4566,22 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s">
         <v>187</v>
       </c>
-      <c r="B63" t="s">
-        <v>188</v>
-      </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" t="s">
+        <v>169</v>
+      </c>
+      <c r="F63" t="s">
         <v>189</v>
-      </c>
-      <c r="E63" t="s">
-        <v>151</v>
-      </c>
-      <c r="F63" t="s">
-        <v>169</v>
       </c>
       <c r="G63" t="s">
         <v>189</v>
@@ -4889,9 +4589,6 @@
       <c r="H63" t="b">
         <v>1</v>
       </c>
-      <c r="I63" t="s">
-        <v>189</v>
-      </c>
       <c r="J63" t="s">
         <v>388</v>
       </c>
@@ -4901,22 +4598,22 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" t="s">
         <v>190</v>
       </c>
-      <c r="B64" t="s">
-        <v>191</v>
-      </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F64" t="s">
         <v>192</v>
-      </c>
-      <c r="E64" t="s">
-        <v>151</v>
-      </c>
-      <c r="F64" t="s">
-        <v>169</v>
       </c>
       <c r="G64" t="s">
         <v>192</v>
@@ -4924,9 +4621,6 @@
       <c r="H64" t="b">
         <v>1</v>
       </c>
-      <c r="I64" t="s">
-        <v>192</v>
-      </c>
       <c r="J64" t="s">
         <v>388</v>
       </c>
@@ -4936,22 +4630,22 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
         <v>193</v>
       </c>
-      <c r="B65" t="s">
-        <v>194</v>
-      </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" t="s">
         <v>195</v>
-      </c>
-      <c r="E65" t="s">
-        <v>151</v>
-      </c>
-      <c r="F65" t="s">
-        <v>169</v>
       </c>
       <c r="G65" t="s">
         <v>195</v>
@@ -4959,9 +4653,6 @@
       <c r="H65" t="b">
         <v>1</v>
       </c>
-      <c r="I65" t="s">
-        <v>195</v>
-      </c>
       <c r="J65" t="s">
         <v>388</v>
       </c>
@@ -4971,22 +4662,22 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" t="s">
         <v>196</v>
       </c>
-      <c r="B66" t="s">
-        <v>197</v>
-      </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" t="s">
+        <v>169</v>
+      </c>
+      <c r="F66" t="s">
         <v>198</v>
-      </c>
-      <c r="E66" t="s">
-        <v>151</v>
-      </c>
-      <c r="F66" t="s">
-        <v>169</v>
       </c>
       <c r="G66" t="s">
         <v>198</v>
@@ -4994,9 +4685,6 @@
       <c r="H66" t="b">
         <v>1</v>
       </c>
-      <c r="I66" t="s">
-        <v>198</v>
-      </c>
       <c r="J66" t="s">
         <v>388</v>
       </c>
@@ -5005,23 +4693,14 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B67" t="s">
-        <v>200</v>
-      </c>
       <c r="C67">
         <v>2</v>
-      </c>
-      <c r="D67" t="s">
-        <v>201</v>
-      </c>
-      <c r="E67" t="s">
-        <v>151</v>
-      </c>
-      <c r="F67" t="s">
-        <v>201</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -5035,22 +4714,22 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" t="s">
         <v>202</v>
       </c>
-      <c r="B68" t="s">
-        <v>203</v>
-      </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" t="s">
+        <v>201</v>
+      </c>
+      <c r="F68" t="s">
         <v>204</v>
-      </c>
-      <c r="E68" t="s">
-        <v>151</v>
-      </c>
-      <c r="F68" t="s">
-        <v>201</v>
       </c>
       <c r="G68" t="s">
         <v>204</v>
@@ -5058,9 +4737,6 @@
       <c r="H68" t="b">
         <v>1</v>
       </c>
-      <c r="I68" t="s">
-        <v>204</v>
-      </c>
       <c r="J68" t="s">
         <v>388</v>
       </c>
@@ -5070,22 +4746,22 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" t="s">
         <v>205</v>
       </c>
-      <c r="B69" t="s">
-        <v>206</v>
-      </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
+        <v>151</v>
+      </c>
+      <c r="E69" t="s">
+        <v>201</v>
+      </c>
+      <c r="F69" t="s">
         <v>207</v>
-      </c>
-      <c r="E69" t="s">
-        <v>151</v>
-      </c>
-      <c r="F69" t="s">
-        <v>201</v>
       </c>
       <c r="G69" t="s">
         <v>207</v>
@@ -5093,9 +4769,6 @@
       <c r="H69" t="b">
         <v>1</v>
       </c>
-      <c r="I69" t="s">
-        <v>207</v>
-      </c>
       <c r="J69" t="s">
         <v>388</v>
       </c>
@@ -5105,22 +4778,22 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" t="s">
         <v>208</v>
       </c>
-      <c r="B70" t="s">
-        <v>209</v>
-      </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
+        <v>151</v>
+      </c>
+      <c r="E70" t="s">
+        <v>201</v>
+      </c>
+      <c r="F70" t="s">
         <v>210</v>
-      </c>
-      <c r="E70" t="s">
-        <v>151</v>
-      </c>
-      <c r="F70" t="s">
-        <v>201</v>
       </c>
       <c r="G70" t="s">
         <v>210</v>
@@ -5128,9 +4801,6 @@
       <c r="H70" t="b">
         <v>1</v>
       </c>
-      <c r="I70" t="s">
-        <v>210</v>
-      </c>
       <c r="J70" t="s">
         <v>388</v>
       </c>
@@ -5140,22 +4810,22 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
         <v>211</v>
       </c>
-      <c r="B71" t="s">
-        <v>212</v>
-      </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" t="s">
+        <v>201</v>
+      </c>
+      <c r="F71" t="s">
         <v>213</v>
-      </c>
-      <c r="E71" t="s">
-        <v>151</v>
-      </c>
-      <c r="F71" t="s">
-        <v>201</v>
       </c>
       <c r="G71" t="s">
         <v>213</v>
@@ -5163,9 +4833,6 @@
       <c r="H71" t="b">
         <v>1</v>
       </c>
-      <c r="I71" t="s">
-        <v>213</v>
-      </c>
       <c r="J71" t="s">
         <v>388</v>
       </c>
@@ -5175,22 +4842,22 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" t="s">
         <v>214</v>
       </c>
-      <c r="B72" t="s">
-        <v>215</v>
-      </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
+        <v>151</v>
+      </c>
+      <c r="E72" t="s">
+        <v>201</v>
+      </c>
+      <c r="F72" t="s">
         <v>216</v>
-      </c>
-      <c r="E72" t="s">
-        <v>151</v>
-      </c>
-      <c r="F72" t="s">
-        <v>201</v>
       </c>
       <c r="G72" t="s">
         <v>216</v>
@@ -5198,9 +4865,6 @@
       <c r="H72" t="b">
         <v>1</v>
       </c>
-      <c r="I72" t="s">
-        <v>216</v>
-      </c>
       <c r="J72" t="s">
         <v>388</v>
       </c>
@@ -5210,22 +4874,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s">
         <v>217</v>
       </c>
-      <c r="B73" t="s">
-        <v>218</v>
-      </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" t="s">
         <v>219</v>
-      </c>
-      <c r="E73" t="s">
-        <v>151</v>
-      </c>
-      <c r="F73" t="s">
-        <v>201</v>
       </c>
       <c r="G73" t="s">
         <v>219</v>
@@ -5233,9 +4897,6 @@
       <c r="H73" t="b">
         <v>1</v>
       </c>
-      <c r="I73" t="s">
-        <v>219</v>
-      </c>
       <c r="J73" t="s">
         <v>388</v>
       </c>
@@ -5245,22 +4906,22 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" t="s">
         <v>220</v>
       </c>
-      <c r="B74" t="s">
-        <v>221</v>
-      </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
+        <v>151</v>
+      </c>
+      <c r="E74" t="s">
+        <v>201</v>
+      </c>
+      <c r="F74" t="s">
         <v>50</v>
-      </c>
-      <c r="E74" t="s">
-        <v>151</v>
-      </c>
-      <c r="F74" t="s">
-        <v>201</v>
       </c>
       <c r="G74" t="s">
         <v>50</v>
@@ -5268,9 +4929,6 @@
       <c r="H74" t="b">
         <v>1</v>
       </c>
-      <c r="I74" t="s">
-        <v>50</v>
-      </c>
       <c r="J74" t="s">
         <v>388</v>
       </c>
@@ -5279,23 +4937,14 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B75" t="s">
-        <v>223</v>
-      </c>
       <c r="C75">
         <v>2</v>
-      </c>
-      <c r="D75" t="s">
-        <v>224</v>
-      </c>
-      <c r="E75" t="s">
-        <v>151</v>
-      </c>
-      <c r="F75" t="s">
-        <v>224</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
@@ -5309,22 +4958,22 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" t="s">
         <v>225</v>
       </c>
-      <c r="B76" t="s">
-        <v>226</v>
-      </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
+        <v>151</v>
+      </c>
+      <c r="E76" t="s">
+        <v>224</v>
+      </c>
+      <c r="F76" t="s">
         <v>227</v>
-      </c>
-      <c r="E76" t="s">
-        <v>151</v>
-      </c>
-      <c r="F76" t="s">
-        <v>224</v>
       </c>
       <c r="G76" t="s">
         <v>227</v>
@@ -5332,9 +4981,6 @@
       <c r="H76" t="b">
         <v>1</v>
       </c>
-      <c r="I76" t="s">
-        <v>227</v>
-      </c>
       <c r="J76" t="s">
         <v>388</v>
       </c>
@@ -5344,22 +4990,22 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" t="s">
         <v>228</v>
       </c>
-      <c r="B77" t="s">
-        <v>229</v>
-      </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
+        <v>151</v>
+      </c>
+      <c r="E77" t="s">
+        <v>224</v>
+      </c>
+      <c r="F77" t="s">
         <v>230</v>
-      </c>
-      <c r="E77" t="s">
-        <v>151</v>
-      </c>
-      <c r="F77" t="s">
-        <v>224</v>
       </c>
       <c r="G77" t="s">
         <v>230</v>
@@ -5367,9 +5013,6 @@
       <c r="H77" t="b">
         <v>1</v>
       </c>
-      <c r="I77" t="s">
-        <v>230</v>
-      </c>
       <c r="J77" t="s">
         <v>388</v>
       </c>
@@ -5379,22 +5022,22 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>232</v>
+      </c>
+      <c r="B78" t="s">
         <v>231</v>
       </c>
-      <c r="B78" t="s">
-        <v>232</v>
-      </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
+        <v>151</v>
+      </c>
+      <c r="E78" t="s">
+        <v>224</v>
+      </c>
+      <c r="F78" t="s">
         <v>50</v>
-      </c>
-      <c r="E78" t="s">
-        <v>151</v>
-      </c>
-      <c r="F78" t="s">
-        <v>224</v>
       </c>
       <c r="G78" t="s">
         <v>50</v>
@@ -5402,9 +5045,6 @@
       <c r="H78" t="b">
         <v>1</v>
       </c>
-      <c r="I78" t="s">
-        <v>50</v>
-      </c>
       <c r="J78" t="s">
         <v>388</v>
       </c>
@@ -5413,23 +5053,14 @@
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B79" t="s">
-        <v>234</v>
-      </c>
       <c r="C79">
         <v>2</v>
-      </c>
-      <c r="D79" t="s">
-        <v>235</v>
-      </c>
-      <c r="E79" t="s">
-        <v>151</v>
-      </c>
-      <c r="F79" t="s">
-        <v>235</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -5443,22 +5074,22 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s">
         <v>236</v>
       </c>
-      <c r="B80" t="s">
-        <v>237</v>
-      </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" t="s">
+        <v>235</v>
+      </c>
+      <c r="F80" t="s">
         <v>238</v>
-      </c>
-      <c r="E80" t="s">
-        <v>151</v>
-      </c>
-      <c r="F80" t="s">
-        <v>235</v>
       </c>
       <c r="G80" t="s">
         <v>238</v>
@@ -5466,9 +5097,6 @@
       <c r="H80" t="b">
         <v>1</v>
       </c>
-      <c r="I80" t="s">
-        <v>238</v>
-      </c>
       <c r="J80" t="s">
         <v>388</v>
       </c>
@@ -5478,22 +5106,22 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" t="s">
         <v>239</v>
       </c>
-      <c r="B81" t="s">
-        <v>240</v>
-      </c>
       <c r="C81">
         <v>3</v>
       </c>
       <c r="D81" t="s">
+        <v>151</v>
+      </c>
+      <c r="E81" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" t="s">
         <v>241</v>
-      </c>
-      <c r="E81" t="s">
-        <v>151</v>
-      </c>
-      <c r="F81" t="s">
-        <v>235</v>
       </c>
       <c r="G81" t="s">
         <v>241</v>
@@ -5501,9 +5129,6 @@
       <c r="H81" t="b">
         <v>1</v>
       </c>
-      <c r="I81" t="s">
-        <v>241</v>
-      </c>
       <c r="J81" t="s">
         <v>388</v>
       </c>
@@ -5513,22 +5138,22 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>243</v>
+      </c>
+      <c r="B82" t="s">
         <v>242</v>
       </c>
-      <c r="B82" t="s">
-        <v>243</v>
-      </c>
       <c r="C82">
         <v>3</v>
       </c>
       <c r="D82" t="s">
+        <v>151</v>
+      </c>
+      <c r="E82" t="s">
+        <v>235</v>
+      </c>
+      <c r="F82" t="s">
         <v>244</v>
-      </c>
-      <c r="E82" t="s">
-        <v>151</v>
-      </c>
-      <c r="F82" t="s">
-        <v>235</v>
       </c>
       <c r="G82" t="s">
         <v>244</v>
@@ -5536,9 +5161,6 @@
       <c r="H82" t="b">
         <v>1</v>
       </c>
-      <c r="I82" t="s">
-        <v>244</v>
-      </c>
       <c r="J82" t="s">
         <v>388</v>
       </c>
@@ -5548,22 +5170,22 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>246</v>
+      </c>
+      <c r="B83" t="s">
         <v>245</v>
       </c>
-      <c r="B83" t="s">
-        <v>246</v>
-      </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" t="s">
+        <v>235</v>
+      </c>
+      <c r="F83" t="s">
         <v>247</v>
-      </c>
-      <c r="E83" t="s">
-        <v>151</v>
-      </c>
-      <c r="F83" t="s">
-        <v>235</v>
       </c>
       <c r="G83" t="s">
         <v>247</v>
@@ -5571,9 +5193,6 @@
       <c r="H83" t="b">
         <v>1</v>
       </c>
-      <c r="I83" t="s">
-        <v>247</v>
-      </c>
       <c r="J83" t="s">
         <v>388</v>
       </c>
@@ -5583,22 +5202,22 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>249</v>
+      </c>
+      <c r="B84" t="s">
         <v>248</v>
       </c>
-      <c r="B84" t="s">
-        <v>249</v>
-      </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
+        <v>151</v>
+      </c>
+      <c r="E84" t="s">
+        <v>235</v>
+      </c>
+      <c r="F84" t="s">
         <v>50</v>
-      </c>
-      <c r="E84" t="s">
-        <v>151</v>
-      </c>
-      <c r="F84" t="s">
-        <v>235</v>
       </c>
       <c r="G84" t="s">
         <v>50</v>
@@ -5606,9 +5225,6 @@
       <c r="H84" t="b">
         <v>1</v>
       </c>
-      <c r="I84" t="s">
-        <v>50</v>
-      </c>
       <c r="J84" t="s">
         <v>388</v>
       </c>
@@ -5617,23 +5233,14 @@
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B85" t="s">
-        <v>251</v>
-      </c>
       <c r="C85">
         <v>2</v>
-      </c>
-      <c r="D85" t="s">
-        <v>252</v>
-      </c>
-      <c r="E85" t="s">
-        <v>151</v>
-      </c>
-      <c r="F85" t="s">
-        <v>252</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
@@ -5647,22 +5254,22 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" t="s">
         <v>253</v>
       </c>
-      <c r="B86" t="s">
-        <v>254</v>
-      </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" t="s">
+        <v>252</v>
+      </c>
+      <c r="F86" t="s">
         <v>255</v>
-      </c>
-      <c r="E86" t="s">
-        <v>151</v>
-      </c>
-      <c r="F86" t="s">
-        <v>252</v>
       </c>
       <c r="G86" t="s">
         <v>255</v>
@@ -5670,9 +5277,6 @@
       <c r="H86" t="b">
         <v>1</v>
       </c>
-      <c r="I86" t="s">
-        <v>255</v>
-      </c>
       <c r="J86" t="s">
         <v>388</v>
       </c>
@@ -5682,22 +5286,22 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" t="s">
         <v>256</v>
       </c>
-      <c r="B87" t="s">
-        <v>257</v>
-      </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" t="s">
+        <v>252</v>
+      </c>
+      <c r="F87" t="s">
         <v>258</v>
-      </c>
-      <c r="E87" t="s">
-        <v>151</v>
-      </c>
-      <c r="F87" t="s">
-        <v>252</v>
       </c>
       <c r="G87" t="s">
         <v>258</v>
@@ -5705,9 +5309,6 @@
       <c r="H87" t="b">
         <v>1</v>
       </c>
-      <c r="I87" t="s">
-        <v>258</v>
-      </c>
       <c r="J87" t="s">
         <v>388</v>
       </c>
@@ -5717,22 +5318,22 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>260</v>
+      </c>
+      <c r="B88" t="s">
         <v>259</v>
       </c>
-      <c r="B88" t="s">
-        <v>260</v>
-      </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
+        <v>151</v>
+      </c>
+      <c r="E88" t="s">
+        <v>252</v>
+      </c>
+      <c r="F88" t="s">
         <v>261</v>
-      </c>
-      <c r="E88" t="s">
-        <v>151</v>
-      </c>
-      <c r="F88" t="s">
-        <v>252</v>
       </c>
       <c r="G88" t="s">
         <v>261</v>
@@ -5740,9 +5341,6 @@
       <c r="H88" t="b">
         <v>1</v>
       </c>
-      <c r="I88" t="s">
-        <v>261</v>
-      </c>
       <c r="J88" t="s">
         <v>388</v>
       </c>
@@ -5752,22 +5350,22 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" t="s">
         <v>262</v>
       </c>
-      <c r="B89" t="s">
-        <v>263</v>
-      </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
+        <v>151</v>
+      </c>
+      <c r="E89" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" t="s">
         <v>264</v>
-      </c>
-      <c r="E89" t="s">
-        <v>151</v>
-      </c>
-      <c r="F89" t="s">
-        <v>252</v>
       </c>
       <c r="G89" t="s">
         <v>264</v>
@@ -5775,9 +5373,6 @@
       <c r="H89" t="b">
         <v>1</v>
       </c>
-      <c r="I89" t="s">
-        <v>264</v>
-      </c>
       <c r="J89" t="s">
         <v>388</v>
       </c>
@@ -5787,22 +5382,22 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s">
         <v>265</v>
       </c>
-      <c r="B90" t="s">
-        <v>266</v>
-      </c>
       <c r="C90">
         <v>3</v>
       </c>
       <c r="D90" t="s">
+        <v>151</v>
+      </c>
+      <c r="E90" t="s">
+        <v>252</v>
+      </c>
+      <c r="F90" t="s">
         <v>267</v>
-      </c>
-      <c r="E90" t="s">
-        <v>151</v>
-      </c>
-      <c r="F90" t="s">
-        <v>252</v>
       </c>
       <c r="G90" t="s">
         <v>267</v>
@@ -5810,9 +5405,6 @@
       <c r="H90" t="b">
         <v>1</v>
       </c>
-      <c r="I90" t="s">
-        <v>267</v>
-      </c>
       <c r="J90" t="s">
         <v>388</v>
       </c>
@@ -5822,22 +5414,22 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>269</v>
+      </c>
+      <c r="B91" t="s">
         <v>268</v>
       </c>
-      <c r="B91" t="s">
-        <v>269</v>
-      </c>
       <c r="C91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
+        <v>151</v>
+      </c>
+      <c r="E91" t="s">
+        <v>252</v>
+      </c>
+      <c r="F91" t="s">
         <v>270</v>
-      </c>
-      <c r="E91" t="s">
-        <v>151</v>
-      </c>
-      <c r="F91" t="s">
-        <v>252</v>
       </c>
       <c r="G91" t="s">
         <v>270</v>
@@ -5845,9 +5437,6 @@
       <c r="H91" t="b">
         <v>1</v>
       </c>
-      <c r="I91" t="s">
-        <v>270</v>
-      </c>
       <c r="J91" t="s">
         <v>388</v>
       </c>
@@ -5856,23 +5445,14 @@
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B92" t="s">
-        <v>272</v>
-      </c>
       <c r="C92">
         <v>2</v>
-      </c>
-      <c r="D92" t="s">
-        <v>273</v>
-      </c>
-      <c r="E92" t="s">
-        <v>151</v>
-      </c>
-      <c r="F92" t="s">
-        <v>273</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -5886,22 +5466,22 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>275</v>
+      </c>
+      <c r="B93" t="s">
         <v>274</v>
       </c>
-      <c r="B93" t="s">
-        <v>275</v>
-      </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E93" t="s">
+        <v>273</v>
+      </c>
+      <c r="F93" t="s">
         <v>276</v>
-      </c>
-      <c r="E93" t="s">
-        <v>151</v>
-      </c>
-      <c r="F93" t="s">
-        <v>273</v>
       </c>
       <c r="G93" t="s">
         <v>276</v>
@@ -5909,9 +5489,6 @@
       <c r="H93" t="b">
         <v>1</v>
       </c>
-      <c r="I93" t="s">
-        <v>276</v>
-      </c>
       <c r="J93" t="s">
         <v>388</v>
       </c>
@@ -5921,22 +5498,22 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>278</v>
+      </c>
+      <c r="B94" t="s">
         <v>277</v>
       </c>
-      <c r="B94" t="s">
-        <v>278</v>
-      </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
+        <v>151</v>
+      </c>
+      <c r="E94" t="s">
+        <v>273</v>
+      </c>
+      <c r="F94" t="s">
         <v>279</v>
-      </c>
-      <c r="E94" t="s">
-        <v>151</v>
-      </c>
-      <c r="F94" t="s">
-        <v>273</v>
       </c>
       <c r="G94" t="s">
         <v>279</v>
@@ -5944,9 +5521,6 @@
       <c r="H94" t="b">
         <v>1</v>
       </c>
-      <c r="I94" t="s">
-        <v>279</v>
-      </c>
       <c r="J94" t="s">
         <v>388</v>
       </c>
@@ -5956,22 +5530,22 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" t="s">
         <v>280</v>
       </c>
-      <c r="B95" t="s">
-        <v>281</v>
-      </c>
       <c r="C95">
         <v>3</v>
       </c>
       <c r="D95" t="s">
+        <v>151</v>
+      </c>
+      <c r="E95" t="s">
+        <v>273</v>
+      </c>
+      <c r="F95" t="s">
         <v>282</v>
-      </c>
-      <c r="E95" t="s">
-        <v>151</v>
-      </c>
-      <c r="F95" t="s">
-        <v>273</v>
       </c>
       <c r="G95" t="s">
         <v>282</v>
@@ -5979,9 +5553,6 @@
       <c r="H95" t="b">
         <v>1</v>
       </c>
-      <c r="I95" t="s">
-        <v>282</v>
-      </c>
       <c r="J95" t="s">
         <v>388</v>
       </c>
@@ -5991,22 +5562,22 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>284</v>
+      </c>
+      <c r="B96" t="s">
         <v>283</v>
       </c>
-      <c r="B96" t="s">
-        <v>284</v>
-      </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
+        <v>151</v>
+      </c>
+      <c r="E96" t="s">
+        <v>273</v>
+      </c>
+      <c r="F96" t="s">
         <v>50</v>
-      </c>
-      <c r="E96" t="s">
-        <v>151</v>
-      </c>
-      <c r="F96" t="s">
-        <v>273</v>
       </c>
       <c r="G96" t="s">
         <v>50</v>
@@ -6014,9 +5585,6 @@
       <c r="H96" t="b">
         <v>1</v>
       </c>
-      <c r="I96" t="s">
-        <v>50</v>
-      </c>
       <c r="J96" t="s">
         <v>388</v>
       </c>
@@ -6026,19 +5594,19 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" t="s">
         <v>285</v>
       </c>
-      <c r="B97" t="s">
-        <v>286</v>
-      </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
+        <v>151</v>
+      </c>
+      <c r="E97" t="s">
         <v>50</v>
-      </c>
-      <c r="E97" t="s">
-        <v>151</v>
       </c>
       <c r="F97" t="s">
         <v>50</v>
@@ -6049,9 +5617,6 @@
       <c r="H97" t="b">
         <v>1</v>
       </c>
-      <c r="I97" t="s">
-        <v>50</v>
-      </c>
       <c r="J97" t="s">
         <v>388</v>
       </c>
@@ -6060,20 +5625,14 @@
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
+        <v>288</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B98" t="s">
-        <v>288</v>
-      </c>
       <c r="C98">
         <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>289</v>
-      </c>
-      <c r="E98" t="s">
-        <v>289</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
@@ -6086,23 +5645,14 @@
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
+        <v>291</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B99" t="s">
-        <v>291</v>
-      </c>
       <c r="C99">
         <v>2</v>
-      </c>
-      <c r="D99" t="s">
-        <v>292</v>
-      </c>
-      <c r="E99" t="s">
-        <v>289</v>
-      </c>
-      <c r="F99" t="s">
-        <v>292</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
@@ -6116,22 +5666,22 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>294</v>
+      </c>
+      <c r="B100" t="s">
         <v>293</v>
       </c>
-      <c r="B100" t="s">
-        <v>294</v>
-      </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" t="s">
+        <v>292</v>
+      </c>
+      <c r="F100" t="s">
         <v>295</v>
-      </c>
-      <c r="E100" t="s">
-        <v>289</v>
-      </c>
-      <c r="F100" t="s">
-        <v>292</v>
       </c>
       <c r="G100" t="s">
         <v>295</v>
@@ -6139,9 +5689,6 @@
       <c r="H100" t="b">
         <v>1</v>
       </c>
-      <c r="I100" t="s">
-        <v>295</v>
-      </c>
       <c r="J100" t="s">
         <v>289</v>
       </c>
@@ -6151,22 +5698,22 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>297</v>
+      </c>
+      <c r="B101" t="s">
         <v>296</v>
       </c>
-      <c r="B101" t="s">
-        <v>297</v>
-      </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
+        <v>289</v>
+      </c>
+      <c r="E101" t="s">
+        <v>292</v>
+      </c>
+      <c r="F101" t="s">
         <v>298</v>
-      </c>
-      <c r="E101" t="s">
-        <v>289</v>
-      </c>
-      <c r="F101" t="s">
-        <v>292</v>
       </c>
       <c r="G101" t="s">
         <v>298</v>
@@ -6174,9 +5721,6 @@
       <c r="H101" t="b">
         <v>1</v>
       </c>
-      <c r="I101" t="s">
-        <v>298</v>
-      </c>
       <c r="J101" t="s">
         <v>289</v>
       </c>
@@ -6186,22 +5730,22 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>300</v>
+      </c>
+      <c r="B102" t="s">
         <v>299</v>
       </c>
-      <c r="B102" t="s">
-        <v>300</v>
-      </c>
       <c r="C102">
         <v>3</v>
       </c>
       <c r="D102" t="s">
+        <v>289</v>
+      </c>
+      <c r="E102" t="s">
+        <v>292</v>
+      </c>
+      <c r="F102" t="s">
         <v>301</v>
-      </c>
-      <c r="E102" t="s">
-        <v>289</v>
-      </c>
-      <c r="F102" t="s">
-        <v>292</v>
       </c>
       <c r="G102" t="s">
         <v>301</v>
@@ -6209,9 +5753,6 @@
       <c r="H102" t="b">
         <v>1</v>
       </c>
-      <c r="I102" t="s">
-        <v>301</v>
-      </c>
       <c r="J102" t="s">
         <v>289</v>
       </c>
@@ -6221,22 +5762,22 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>303</v>
+      </c>
+      <c r="B103" t="s">
         <v>302</v>
       </c>
-      <c r="B103" t="s">
-        <v>303</v>
-      </c>
       <c r="C103">
         <v>3</v>
       </c>
       <c r="D103" t="s">
+        <v>289</v>
+      </c>
+      <c r="E103" t="s">
+        <v>292</v>
+      </c>
+      <c r="F103" t="s">
         <v>304</v>
-      </c>
-      <c r="E103" t="s">
-        <v>289</v>
-      </c>
-      <c r="F103" t="s">
-        <v>292</v>
       </c>
       <c r="G103" t="s">
         <v>304</v>
@@ -6244,9 +5785,6 @@
       <c r="H103" t="b">
         <v>1</v>
       </c>
-      <c r="I103" t="s">
-        <v>304</v>
-      </c>
       <c r="J103" t="s">
         <v>289</v>
       </c>
@@ -6255,23 +5793,14 @@
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
+        <v>306</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B104" t="s">
-        <v>306</v>
-      </c>
       <c r="C104">
         <v>2</v>
-      </c>
-      <c r="D104" t="s">
-        <v>307</v>
-      </c>
-      <c r="E104" t="s">
-        <v>289</v>
-      </c>
-      <c r="F104" t="s">
-        <v>307</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
@@ -6285,22 +5814,22 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>309</v>
+      </c>
+      <c r="B105" t="s">
         <v>308</v>
       </c>
-      <c r="B105" t="s">
-        <v>309</v>
-      </c>
       <c r="C105">
         <v>3</v>
       </c>
       <c r="D105" t="s">
+        <v>289</v>
+      </c>
+      <c r="E105" t="s">
+        <v>307</v>
+      </c>
+      <c r="F105" t="s">
         <v>295</v>
-      </c>
-      <c r="E105" t="s">
-        <v>289</v>
-      </c>
-      <c r="F105" t="s">
-        <v>307</v>
       </c>
       <c r="G105" t="s">
         <v>295</v>
@@ -6308,9 +5837,6 @@
       <c r="H105" t="b">
         <v>1</v>
       </c>
-      <c r="I105" t="s">
-        <v>295</v>
-      </c>
       <c r="J105" t="s">
         <v>289</v>
       </c>
@@ -6320,22 +5846,22 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>311</v>
+      </c>
+      <c r="B106" t="s">
         <v>310</v>
       </c>
-      <c r="B106" t="s">
-        <v>311</v>
-      </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
+        <v>289</v>
+      </c>
+      <c r="E106" t="s">
+        <v>307</v>
+      </c>
+      <c r="F106" t="s">
         <v>298</v>
-      </c>
-      <c r="E106" t="s">
-        <v>289</v>
-      </c>
-      <c r="F106" t="s">
-        <v>307</v>
       </c>
       <c r="G106" t="s">
         <v>298</v>
@@ -6343,9 +5869,6 @@
       <c r="H106" t="b">
         <v>1</v>
       </c>
-      <c r="I106" t="s">
-        <v>298</v>
-      </c>
       <c r="J106" t="s">
         <v>289</v>
       </c>
@@ -6355,22 +5878,22 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>313</v>
+      </c>
+      <c r="B107" t="s">
         <v>312</v>
       </c>
-      <c r="B107" t="s">
-        <v>313</v>
-      </c>
       <c r="C107">
         <v>3</v>
       </c>
       <c r="D107" t="s">
+        <v>289</v>
+      </c>
+      <c r="E107" t="s">
+        <v>307</v>
+      </c>
+      <c r="F107" t="s">
         <v>301</v>
-      </c>
-      <c r="E107" t="s">
-        <v>289</v>
-      </c>
-      <c r="F107" t="s">
-        <v>307</v>
       </c>
       <c r="G107" t="s">
         <v>301</v>
@@ -6378,9 +5901,6 @@
       <c r="H107" t="b">
         <v>1</v>
       </c>
-      <c r="I107" t="s">
-        <v>301</v>
-      </c>
       <c r="J107" t="s">
         <v>289</v>
       </c>
@@ -6390,22 +5910,22 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>315</v>
+      </c>
+      <c r="B108" t="s">
         <v>314</v>
       </c>
-      <c r="B108" t="s">
-        <v>315</v>
-      </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
+        <v>289</v>
+      </c>
+      <c r="E108" t="s">
+        <v>307</v>
+      </c>
+      <c r="F108" t="s">
         <v>304</v>
-      </c>
-      <c r="E108" t="s">
-        <v>289</v>
-      </c>
-      <c r="F108" t="s">
-        <v>307</v>
       </c>
       <c r="G108" t="s">
         <v>304</v>
@@ -6413,9 +5933,6 @@
       <c r="H108" t="b">
         <v>1</v>
       </c>
-      <c r="I108" t="s">
-        <v>304</v>
-      </c>
       <c r="J108" t="s">
         <v>289</v>
       </c>
@@ -6425,22 +5942,22 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
         <v>316</v>
       </c>
-      <c r="B109" t="s">
-        <v>317</v>
-      </c>
       <c r="C109">
         <v>3</v>
       </c>
       <c r="D109" t="s">
+        <v>289</v>
+      </c>
+      <c r="E109" t="s">
+        <v>307</v>
+      </c>
+      <c r="F109" t="s">
         <v>318</v>
-      </c>
-      <c r="E109" t="s">
-        <v>289</v>
-      </c>
-      <c r="F109" t="s">
-        <v>307</v>
       </c>
       <c r="G109" t="s">
         <v>318</v>
@@ -6448,9 +5965,6 @@
       <c r="H109" t="b">
         <v>1</v>
       </c>
-      <c r="I109" t="s">
-        <v>318</v>
-      </c>
       <c r="J109" t="s">
         <v>289</v>
       </c>
@@ -6460,19 +5974,19 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>320</v>
+      </c>
+      <c r="B110" t="s">
         <v>319</v>
       </c>
-      <c r="B110" t="s">
-        <v>320</v>
-      </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
+        <v>289</v>
+      </c>
+      <c r="E110" t="s">
         <v>321</v>
-      </c>
-      <c r="E110" t="s">
-        <v>289</v>
       </c>
       <c r="F110" t="s">
         <v>321</v>
@@ -6483,9 +5997,6 @@
       <c r="H110" t="b">
         <v>1</v>
       </c>
-      <c r="I110" t="s">
-        <v>321</v>
-      </c>
       <c r="J110" t="s">
         <v>289</v>
       </c>
@@ -6495,19 +6006,19 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>323</v>
+      </c>
+      <c r="B111" t="s">
         <v>322</v>
       </c>
-      <c r="B111" t="s">
-        <v>323</v>
-      </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
+        <v>289</v>
+      </c>
+      <c r="E111" t="s">
         <v>324</v>
-      </c>
-      <c r="E111" t="s">
-        <v>289</v>
       </c>
       <c r="F111" t="s">
         <v>324</v>
@@ -6518,9 +6029,6 @@
       <c r="H111" t="b">
         <v>1</v>
       </c>
-      <c r="I111" t="s">
-        <v>324</v>
-      </c>
       <c r="J111" t="s">
         <v>289</v>
       </c>
@@ -6530,19 +6038,19 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>326</v>
+      </c>
+      <c r="B112" t="s">
         <v>325</v>
       </c>
-      <c r="B112" t="s">
-        <v>326</v>
-      </c>
       <c r="C112">
         <v>2</v>
       </c>
       <c r="D112" t="s">
+        <v>289</v>
+      </c>
+      <c r="E112" t="s">
         <v>327</v>
-      </c>
-      <c r="E112" t="s">
-        <v>289</v>
       </c>
       <c r="F112" t="s">
         <v>327</v>
@@ -6553,9 +6061,6 @@
       <c r="H112" t="b">
         <v>1</v>
       </c>
-      <c r="I112" t="s">
-        <v>327</v>
-      </c>
       <c r="J112" t="s">
         <v>289</v>
       </c>
@@ -6565,19 +6070,19 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>329</v>
+      </c>
+      <c r="B113" t="s">
         <v>328</v>
       </c>
-      <c r="B113" t="s">
-        <v>329</v>
-      </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
+        <v>289</v>
+      </c>
+      <c r="E113" t="s">
         <v>330</v>
-      </c>
-      <c r="E113" t="s">
-        <v>289</v>
       </c>
       <c r="F113" t="s">
         <v>330</v>
@@ -6588,9 +6093,6 @@
       <c r="H113" t="b">
         <v>1</v>
       </c>
-      <c r="I113" t="s">
-        <v>330</v>
-      </c>
       <c r="J113" t="s">
         <v>289</v>
       </c>
@@ -6600,19 +6102,19 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>332</v>
+      </c>
+      <c r="B114" t="s">
         <v>331</v>
       </c>
-      <c r="B114" t="s">
-        <v>332</v>
-      </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
+        <v>289</v>
+      </c>
+      <c r="E114" t="s">
         <v>333</v>
-      </c>
-      <c r="E114" t="s">
-        <v>289</v>
       </c>
       <c r="F114" t="s">
         <v>333</v>
@@ -6623,9 +6125,6 @@
       <c r="H114" t="b">
         <v>1</v>
       </c>
-      <c r="I114" t="s">
-        <v>333</v>
-      </c>
       <c r="J114" t="s">
         <v>289</v>
       </c>
@@ -6635,19 +6134,19 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>335</v>
+      </c>
+      <c r="B115" t="s">
         <v>334</v>
       </c>
-      <c r="B115" t="s">
-        <v>335</v>
-      </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
+        <v>289</v>
+      </c>
+      <c r="E115" t="s">
         <v>336</v>
-      </c>
-      <c r="E115" t="s">
-        <v>289</v>
       </c>
       <c r="F115" t="s">
         <v>336</v>
@@ -6658,9 +6157,6 @@
       <c r="H115" t="b">
         <v>1</v>
       </c>
-      <c r="I115" t="s">
-        <v>336</v>
-      </c>
       <c r="J115" t="s">
         <v>289</v>
       </c>
@@ -6670,19 +6166,19 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>338</v>
+      </c>
+      <c r="B116" t="s">
         <v>337</v>
       </c>
-      <c r="B116" t="s">
-        <v>338</v>
-      </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
+        <v>289</v>
+      </c>
+      <c r="E116" t="s">
         <v>339</v>
-      </c>
-      <c r="E116" t="s">
-        <v>289</v>
       </c>
       <c r="F116" t="s">
         <v>339</v>
@@ -6693,9 +6189,6 @@
       <c r="H116" t="b">
         <v>1</v>
       </c>
-      <c r="I116" t="s">
-        <v>339</v>
-      </c>
       <c r="J116" t="s">
         <v>289</v>
       </c>
@@ -6705,19 +6198,19 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>341</v>
+      </c>
+      <c r="B117" t="s">
         <v>340</v>
       </c>
-      <c r="B117" t="s">
-        <v>341</v>
-      </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
+        <v>289</v>
+      </c>
+      <c r="E117" t="s">
         <v>50</v>
-      </c>
-      <c r="E117" t="s">
-        <v>289</v>
       </c>
       <c r="F117" t="s">
         <v>50</v>
@@ -6728,9 +6221,6 @@
       <c r="H117" t="b">
         <v>1</v>
       </c>
-      <c r="I117" t="s">
-        <v>50</v>
-      </c>
       <c r="J117" t="s">
         <v>289</v>
       </c>
@@ -6739,20 +6229,14 @@
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
+        <v>343</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B118" t="s">
-        <v>343</v>
-      </c>
       <c r="C118">
         <v>1</v>
-      </c>
-      <c r="D118" t="s">
-        <v>344</v>
-      </c>
-      <c r="E118" t="s">
-        <v>344</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
@@ -6766,19 +6250,19 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>346</v>
+      </c>
+      <c r="B119" t="s">
         <v>345</v>
       </c>
-      <c r="B119" t="s">
-        <v>346</v>
-      </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
+        <v>344</v>
+      </c>
+      <c r="E119" t="s">
         <v>347</v>
-      </c>
-      <c r="E119" t="s">
-        <v>344</v>
       </c>
       <c r="F119" t="s">
         <v>347</v>
@@ -6789,9 +6273,6 @@
       <c r="H119" t="b">
         <v>1</v>
       </c>
-      <c r="I119" t="s">
-        <v>347</v>
-      </c>
       <c r="J119" t="s">
         <v>399</v>
       </c>
@@ -6801,19 +6282,19 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>349</v>
+      </c>
+      <c r="B120" t="s">
         <v>348</v>
       </c>
-      <c r="B120" t="s">
-        <v>349</v>
-      </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
+        <v>344</v>
+      </c>
+      <c r="E120" t="s">
         <v>350</v>
-      </c>
-      <c r="E120" t="s">
-        <v>344</v>
       </c>
       <c r="F120" t="s">
         <v>350</v>
@@ -6824,9 +6305,6 @@
       <c r="H120" t="b">
         <v>1</v>
       </c>
-      <c r="I120" t="s">
-        <v>350</v>
-      </c>
       <c r="J120" t="s">
         <v>399</v>
       </c>
@@ -6836,19 +6314,19 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>352</v>
+      </c>
+      <c r="B121" t="s">
         <v>351</v>
       </c>
-      <c r="B121" t="s">
-        <v>352</v>
-      </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
+        <v>344</v>
+      </c>
+      <c r="E121" t="s">
         <v>353</v>
-      </c>
-      <c r="E121" t="s">
-        <v>344</v>
       </c>
       <c r="F121" t="s">
         <v>353</v>
@@ -6859,9 +6337,6 @@
       <c r="H121" t="b">
         <v>1</v>
       </c>
-      <c r="I121" t="s">
-        <v>353</v>
-      </c>
       <c r="J121" t="s">
         <v>399</v>
       </c>
@@ -6871,19 +6346,19 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>355</v>
+      </c>
+      <c r="B122" t="s">
         <v>354</v>
       </c>
-      <c r="B122" t="s">
-        <v>355</v>
-      </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
+        <v>344</v>
+      </c>
+      <c r="E122" t="s">
         <v>356</v>
-      </c>
-      <c r="E122" t="s">
-        <v>344</v>
       </c>
       <c r="F122" t="s">
         <v>356</v>
@@ -6894,9 +6369,6 @@
       <c r="H122" t="b">
         <v>1</v>
       </c>
-      <c r="I122" t="s">
-        <v>356</v>
-      </c>
       <c r="J122" t="s">
         <v>399</v>
       </c>
@@ -6906,19 +6378,19 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>358</v>
+      </c>
+      <c r="B123" t="s">
         <v>357</v>
       </c>
-      <c r="B123" t="s">
-        <v>358</v>
-      </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
+        <v>344</v>
+      </c>
+      <c r="E123" t="s">
         <v>359</v>
-      </c>
-      <c r="E123" t="s">
-        <v>344</v>
       </c>
       <c r="F123" t="s">
         <v>359</v>
@@ -6929,9 +6401,6 @@
       <c r="H123" t="b">
         <v>1</v>
       </c>
-      <c r="I123" t="s">
-        <v>359</v>
-      </c>
       <c r="J123" t="s">
         <v>399</v>
       </c>
@@ -6941,19 +6410,19 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>361</v>
+      </c>
+      <c r="B124" t="s">
         <v>360</v>
       </c>
-      <c r="B124" t="s">
-        <v>361</v>
-      </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
+        <v>344</v>
+      </c>
+      <c r="E124" t="s">
         <v>362</v>
-      </c>
-      <c r="E124" t="s">
-        <v>344</v>
       </c>
       <c r="F124" t="s">
         <v>362</v>
@@ -6964,9 +6433,6 @@
       <c r="H124" t="b">
         <v>1</v>
       </c>
-      <c r="I124" t="s">
-        <v>362</v>
-      </c>
       <c r="J124" t="s">
         <v>399</v>
       </c>
@@ -6976,19 +6442,19 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>364</v>
+      </c>
+      <c r="B125" t="s">
         <v>363</v>
       </c>
-      <c r="B125" t="s">
-        <v>364</v>
-      </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
+        <v>344</v>
+      </c>
+      <c r="E125" t="s">
         <v>365</v>
-      </c>
-      <c r="E125" t="s">
-        <v>344</v>
       </c>
       <c r="F125" t="s">
         <v>365</v>
@@ -6999,9 +6465,6 @@
       <c r="H125" t="b">
         <v>1</v>
       </c>
-      <c r="I125" t="s">
-        <v>365</v>
-      </c>
       <c r="J125" t="s">
         <v>399</v>
       </c>
@@ -7011,19 +6474,19 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>367</v>
+      </c>
+      <c r="B126" t="s">
         <v>366</v>
       </c>
-      <c r="B126" t="s">
-        <v>367</v>
-      </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
+        <v>344</v>
+      </c>
+      <c r="E126" t="s">
         <v>50</v>
-      </c>
-      <c r="E126" t="s">
-        <v>344</v>
       </c>
       <c r="F126" t="s">
         <v>50</v>
@@ -7034,9 +6497,6 @@
       <c r="H126" t="b">
         <v>1</v>
       </c>
-      <c r="I126" t="s">
-        <v>50</v>
-      </c>
       <c r="J126" t="s">
         <v>399</v>
       </c>
@@ -7046,19 +6506,19 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>396</v>
+      </c>
+      <c r="B127" t="s">
         <v>397</v>
       </c>
-      <c r="B127" t="s">
-        <v>396</v>
-      </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
+        <v>344</v>
+      </c>
+      <c r="E127" t="s">
         <v>398</v>
-      </c>
-      <c r="E127" t="s">
-        <v>344</v>
       </c>
       <c r="F127" t="s">
         <v>398</v>
@@ -7069,9 +6529,6 @@
       <c r="H127" t="b">
         <v>1</v>
       </c>
-      <c r="I127" t="s">
-        <v>398</v>
-      </c>
       <c r="J127" t="s">
         <v>399</v>
       </c>
@@ -7080,20 +6537,14 @@
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
+        <v>369</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B128" t="s">
-        <v>369</v>
-      </c>
       <c r="C128">
         <v>1</v>
-      </c>
-      <c r="D128" t="s">
-        <v>370</v>
-      </c>
-      <c r="E128" t="s">
-        <v>370</v>
       </c>
       <c r="H128" t="b">
         <v>0</v>
@@ -7107,19 +6558,19 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>372</v>
+      </c>
+      <c r="B129" t="s">
         <v>371</v>
       </c>
-      <c r="B129" t="s">
-        <v>372</v>
-      </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
+        <v>370</v>
+      </c>
+      <c r="E129" t="s">
         <v>373</v>
-      </c>
-      <c r="E129" t="s">
-        <v>370</v>
       </c>
       <c r="F129" t="s">
         <v>373</v>
@@ -7130,9 +6581,6 @@
       <c r="H129" t="b">
         <v>1</v>
       </c>
-      <c r="I129" t="s">
-        <v>373</v>
-      </c>
       <c r="J129" t="s">
         <v>370</v>
       </c>
@@ -7142,19 +6590,19 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>375</v>
+      </c>
+      <c r="B130" t="s">
         <v>374</v>
       </c>
-      <c r="B130" t="s">
-        <v>375</v>
-      </c>
       <c r="C130">
         <v>2</v>
       </c>
       <c r="D130" t="s">
+        <v>370</v>
+      </c>
+      <c r="E130" t="s">
         <v>376</v>
-      </c>
-      <c r="E130" t="s">
-        <v>370</v>
       </c>
       <c r="F130" t="s">
         <v>376</v>
@@ -7165,9 +6613,6 @@
       <c r="H130" t="b">
         <v>1</v>
       </c>
-      <c r="I130" t="s">
-        <v>376</v>
-      </c>
       <c r="J130" t="s">
         <v>370</v>
       </c>
@@ -7177,19 +6622,19 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>378</v>
+      </c>
+      <c r="B131" t="s">
         <v>377</v>
       </c>
-      <c r="B131" t="s">
-        <v>378</v>
-      </c>
       <c r="C131">
         <v>2</v>
       </c>
       <c r="D131" t="s">
+        <v>370</v>
+      </c>
+      <c r="E131" t="s">
         <v>379</v>
-      </c>
-      <c r="E131" t="s">
-        <v>370</v>
       </c>
       <c r="F131" t="s">
         <v>379</v>
@@ -7200,9 +6645,6 @@
       <c r="H131" t="b">
         <v>1</v>
       </c>
-      <c r="I131" t="s">
-        <v>379</v>
-      </c>
       <c r="J131" t="s">
         <v>370</v>
       </c>
@@ -7212,19 +6654,19 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>381</v>
+      </c>
+      <c r="B132" t="s">
         <v>380</v>
       </c>
-      <c r="B132" t="s">
-        <v>381</v>
-      </c>
       <c r="C132">
         <v>2</v>
       </c>
       <c r="D132" t="s">
+        <v>370</v>
+      </c>
+      <c r="E132" t="s">
         <v>382</v>
-      </c>
-      <c r="E132" t="s">
-        <v>370</v>
       </c>
       <c r="F132" t="s">
         <v>382</v>
@@ -7235,9 +6677,6 @@
       <c r="H132" t="b">
         <v>1</v>
       </c>
-      <c r="I132" t="s">
-        <v>382</v>
-      </c>
       <c r="J132" t="s">
         <v>370</v>
       </c>
@@ -7247,19 +6686,19 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>384</v>
+      </c>
+      <c r="B133" t="s">
         <v>383</v>
       </c>
-      <c r="B133" t="s">
-        <v>384</v>
-      </c>
       <c r="C133">
         <v>2</v>
       </c>
       <c r="D133" t="s">
+        <v>370</v>
+      </c>
+      <c r="E133" t="s">
         <v>50</v>
-      </c>
-      <c r="E133" t="s">
-        <v>370</v>
       </c>
       <c r="F133" t="s">
         <v>50</v>
@@ -7270,9 +6709,6 @@
       <c r="H133" t="b">
         <v>1</v>
       </c>
-      <c r="I133" t="s">
-        <v>50</v>
-      </c>
       <c r="J133" t="s">
         <v>370</v>
       </c>
@@ -7282,19 +6718,19 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>386</v>
+      </c>
+      <c r="B134" t="s">
         <v>385</v>
       </c>
-      <c r="B134" t="s">
-        <v>386</v>
-      </c>
       <c r="C134">
         <v>2</v>
       </c>
       <c r="D134" t="s">
+        <v>370</v>
+      </c>
+      <c r="E134" t="s">
         <v>124</v>
-      </c>
-      <c r="E134" t="s">
-        <v>370</v>
       </c>
       <c r="F134" t="s">
         <v>124</v>
@@ -7305,9 +6741,6 @@
       <c r="H134" t="b">
         <v>1</v>
       </c>
-      <c r="I134" t="s">
-        <v>124</v>
-      </c>
       <c r="J134" t="s">
         <v>370</v>
       </c>
@@ -7317,10 +6750,10 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>390</v>
+      </c>
+      <c r="B135" t="s">
         <v>389</v>
-      </c>
-      <c r="B135" t="s">
-        <v>390</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7339,9 +6772,6 @@
       </c>
       <c r="H135" t="b">
         <v>1</v>
-      </c>
-      <c r="I135" t="s">
-        <v>50</v>
       </c>
       <c r="J135" t="s">
         <v>370</v>
@@ -7354,4 +6784,4125 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K135"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="75.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
+    <col min="6" max="6" width="62.7109375" customWidth="1"/>
+    <col min="7" max="7" width="54.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>387</v>
+      </c>
+      <c r="K1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>391</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>391</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>391</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>391</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>392</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>392</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>392</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>392</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>392</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>393</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>393</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>393</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>393</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>393</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>393</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>394</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>394</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>394</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>394</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>394</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>395</v>
+      </c>
+      <c r="K27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>395</v>
+      </c>
+      <c r="K28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>395</v>
+      </c>
+      <c r="K29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>395</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>395</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>395</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>395</v>
+      </c>
+      <c r="K33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
+        <v>395</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>395</v>
+      </c>
+      <c r="K35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>395</v>
+      </c>
+      <c r="K36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>395</v>
+      </c>
+      <c r="K37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="s">
+        <v>395</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
+        <v>395</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" t="s">
+        <v>50</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
+        <v>395</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G45" t="s">
+        <v>136</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" t="s">
+        <v>139</v>
+      </c>
+      <c r="G46" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
+        <v>142</v>
+      </c>
+      <c r="G49" t="s">
+        <v>148</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" t="s">
+        <v>154</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>388</v>
+      </c>
+      <c r="K51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" t="s">
+        <v>157</v>
+      </c>
+      <c r="G52" t="s">
+        <v>157</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>388</v>
+      </c>
+      <c r="K52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E53" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" t="s">
+        <v>160</v>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>388</v>
+      </c>
+      <c r="K53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>151</v>
+      </c>
+      <c r="E54" t="s">
+        <v>154</v>
+      </c>
+      <c r="F54" t="s">
+        <v>163</v>
+      </c>
+      <c r="G54" t="s">
+        <v>163</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>388</v>
+      </c>
+      <c r="K54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" t="s">
+        <v>154</v>
+      </c>
+      <c r="F55" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" t="s">
+        <v>166</v>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
+        <v>388</v>
+      </c>
+      <c r="K55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>151</v>
+      </c>
+      <c r="E56" t="s">
+        <v>169</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>388</v>
+      </c>
+      <c r="K56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>169</v>
+      </c>
+      <c r="F57" t="s">
+        <v>172</v>
+      </c>
+      <c r="G57" t="s">
+        <v>172</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>388</v>
+      </c>
+      <c r="K57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" t="s">
+        <v>169</v>
+      </c>
+      <c r="F58" t="s">
+        <v>50</v>
+      </c>
+      <c r="G58" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
+        <v>388</v>
+      </c>
+      <c r="K58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" t="s">
+        <v>169</v>
+      </c>
+      <c r="F59" t="s">
+        <v>177</v>
+      </c>
+      <c r="G59" t="s">
+        <v>177</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>388</v>
+      </c>
+      <c r="K59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" t="s">
+        <v>169</v>
+      </c>
+      <c r="F60" t="s">
+        <v>180</v>
+      </c>
+      <c r="G60" t="s">
+        <v>180</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>388</v>
+      </c>
+      <c r="K60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+      <c r="E61" t="s">
+        <v>169</v>
+      </c>
+      <c r="F61" t="s">
+        <v>183</v>
+      </c>
+      <c r="G61" t="s">
+        <v>183</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
+        <v>388</v>
+      </c>
+      <c r="K61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E62" t="s">
+        <v>169</v>
+      </c>
+      <c r="F62" t="s">
+        <v>186</v>
+      </c>
+      <c r="G62" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
+        <v>388</v>
+      </c>
+      <c r="K62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" t="s">
+        <v>169</v>
+      </c>
+      <c r="F63" t="s">
+        <v>189</v>
+      </c>
+      <c r="G63" t="s">
+        <v>189</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>388</v>
+      </c>
+      <c r="K63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F64" t="s">
+        <v>192</v>
+      </c>
+      <c r="G64" t="s">
+        <v>192</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>388</v>
+      </c>
+      <c r="K64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" t="s">
+        <v>195</v>
+      </c>
+      <c r="G65" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
+        <v>388</v>
+      </c>
+      <c r="K65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" t="s">
+        <v>169</v>
+      </c>
+      <c r="F66" t="s">
+        <v>198</v>
+      </c>
+      <c r="G66" t="s">
+        <v>198</v>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="s">
+        <v>388</v>
+      </c>
+      <c r="K66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" t="s">
+        <v>201</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
+        <v>388</v>
+      </c>
+      <c r="K67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" t="s">
+        <v>201</v>
+      </c>
+      <c r="F68" t="s">
+        <v>204</v>
+      </c>
+      <c r="G68" t="s">
+        <v>204</v>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="s">
+        <v>388</v>
+      </c>
+      <c r="K68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>151</v>
+      </c>
+      <c r="E69" t="s">
+        <v>201</v>
+      </c>
+      <c r="F69" t="s">
+        <v>207</v>
+      </c>
+      <c r="G69" t="s">
+        <v>207</v>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="s">
+        <v>388</v>
+      </c>
+      <c r="K69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>151</v>
+      </c>
+      <c r="E70" t="s">
+        <v>201</v>
+      </c>
+      <c r="F70" t="s">
+        <v>210</v>
+      </c>
+      <c r="G70" t="s">
+        <v>210</v>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="s">
+        <v>388</v>
+      </c>
+      <c r="K70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" t="s">
+        <v>201</v>
+      </c>
+      <c r="F71" t="s">
+        <v>213</v>
+      </c>
+      <c r="G71" t="s">
+        <v>213</v>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="s">
+        <v>388</v>
+      </c>
+      <c r="K71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>151</v>
+      </c>
+      <c r="E72" t="s">
+        <v>201</v>
+      </c>
+      <c r="F72" t="s">
+        <v>216</v>
+      </c>
+      <c r="G72" t="s">
+        <v>216</v>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="s">
+        <v>388</v>
+      </c>
+      <c r="K72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" t="s">
+        <v>219</v>
+      </c>
+      <c r="G73" t="s">
+        <v>219</v>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="s">
+        <v>388</v>
+      </c>
+      <c r="K73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>151</v>
+      </c>
+      <c r="E74" t="s">
+        <v>201</v>
+      </c>
+      <c r="F74" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
+        <v>388</v>
+      </c>
+      <c r="K74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>151</v>
+      </c>
+      <c r="E75" t="s">
+        <v>224</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>388</v>
+      </c>
+      <c r="K75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>151</v>
+      </c>
+      <c r="E76" t="s">
+        <v>224</v>
+      </c>
+      <c r="F76" t="s">
+        <v>227</v>
+      </c>
+      <c r="G76" t="s">
+        <v>227</v>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="s">
+        <v>388</v>
+      </c>
+      <c r="K76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>151</v>
+      </c>
+      <c r="E77" t="s">
+        <v>224</v>
+      </c>
+      <c r="F77" t="s">
+        <v>230</v>
+      </c>
+      <c r="G77" t="s">
+        <v>230</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>388</v>
+      </c>
+      <c r="K77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>232</v>
+      </c>
+      <c r="B78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>151</v>
+      </c>
+      <c r="E78" t="s">
+        <v>224</v>
+      </c>
+      <c r="F78" t="s">
+        <v>50</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="s">
+        <v>388</v>
+      </c>
+      <c r="K78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>151</v>
+      </c>
+      <c r="E79" t="s">
+        <v>235</v>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>388</v>
+      </c>
+      <c r="K79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" t="s">
+        <v>235</v>
+      </c>
+      <c r="F80" t="s">
+        <v>238</v>
+      </c>
+      <c r="G80" t="s">
+        <v>238</v>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="s">
+        <v>388</v>
+      </c>
+      <c r="K80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>151</v>
+      </c>
+      <c r="E81" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" t="s">
+        <v>241</v>
+      </c>
+      <c r="G81" t="s">
+        <v>241</v>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="s">
+        <v>388</v>
+      </c>
+      <c r="K81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>243</v>
+      </c>
+      <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="s">
+        <v>151</v>
+      </c>
+      <c r="E82" t="s">
+        <v>235</v>
+      </c>
+      <c r="F82" t="s">
+        <v>244</v>
+      </c>
+      <c r="G82" t="s">
+        <v>244</v>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="s">
+        <v>388</v>
+      </c>
+      <c r="K82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>246</v>
+      </c>
+      <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" t="s">
+        <v>235</v>
+      </c>
+      <c r="F83" t="s">
+        <v>247</v>
+      </c>
+      <c r="G83" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>388</v>
+      </c>
+      <c r="K83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>249</v>
+      </c>
+      <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>151</v>
+      </c>
+      <c r="E84" t="s">
+        <v>235</v>
+      </c>
+      <c r="F84" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="s">
+        <v>388</v>
+      </c>
+      <c r="K84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" t="s">
+        <v>252</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>388</v>
+      </c>
+      <c r="K85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" t="s">
+        <v>253</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" t="s">
+        <v>252</v>
+      </c>
+      <c r="F86" t="s">
+        <v>255</v>
+      </c>
+      <c r="G86" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="s">
+        <v>388</v>
+      </c>
+      <c r="K86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" t="s">
+        <v>256</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" t="s">
+        <v>252</v>
+      </c>
+      <c r="F87" t="s">
+        <v>258</v>
+      </c>
+      <c r="G87" t="s">
+        <v>258</v>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="s">
+        <v>388</v>
+      </c>
+      <c r="K87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>260</v>
+      </c>
+      <c r="B88" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>151</v>
+      </c>
+      <c r="E88" t="s">
+        <v>252</v>
+      </c>
+      <c r="F88" t="s">
+        <v>261</v>
+      </c>
+      <c r="G88" t="s">
+        <v>261</v>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
+        <v>388</v>
+      </c>
+      <c r="K88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" t="s">
+        <v>262</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>151</v>
+      </c>
+      <c r="E89" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" t="s">
+        <v>264</v>
+      </c>
+      <c r="G89" t="s">
+        <v>264</v>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
+        <v>388</v>
+      </c>
+      <c r="K89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>151</v>
+      </c>
+      <c r="E90" t="s">
+        <v>252</v>
+      </c>
+      <c r="F90" t="s">
+        <v>267</v>
+      </c>
+      <c r="G90" t="s">
+        <v>267</v>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="s">
+        <v>388</v>
+      </c>
+      <c r="K90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>269</v>
+      </c>
+      <c r="B91" t="s">
+        <v>268</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="s">
+        <v>151</v>
+      </c>
+      <c r="E91" t="s">
+        <v>252</v>
+      </c>
+      <c r="F91" t="s">
+        <v>270</v>
+      </c>
+      <c r="G91" t="s">
+        <v>270</v>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="s">
+        <v>388</v>
+      </c>
+      <c r="K91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>151</v>
+      </c>
+      <c r="E92" t="s">
+        <v>273</v>
+      </c>
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>388</v>
+      </c>
+      <c r="K92">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>275</v>
+      </c>
+      <c r="B93" t="s">
+        <v>274</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E93" t="s">
+        <v>273</v>
+      </c>
+      <c r="F93" t="s">
+        <v>276</v>
+      </c>
+      <c r="G93" t="s">
+        <v>276</v>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="s">
+        <v>388</v>
+      </c>
+      <c r="K93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>278</v>
+      </c>
+      <c r="B94" t="s">
+        <v>277</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>151</v>
+      </c>
+      <c r="E94" t="s">
+        <v>273</v>
+      </c>
+      <c r="F94" t="s">
+        <v>279</v>
+      </c>
+      <c r="G94" t="s">
+        <v>279</v>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="s">
+        <v>388</v>
+      </c>
+      <c r="K94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>151</v>
+      </c>
+      <c r="E95" t="s">
+        <v>273</v>
+      </c>
+      <c r="F95" t="s">
+        <v>282</v>
+      </c>
+      <c r="G95" t="s">
+        <v>282</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>388</v>
+      </c>
+      <c r="K95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>284</v>
+      </c>
+      <c r="B96" t="s">
+        <v>283</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>151</v>
+      </c>
+      <c r="E96" t="s">
+        <v>273</v>
+      </c>
+      <c r="F96" t="s">
+        <v>50</v>
+      </c>
+      <c r="G96" t="s">
+        <v>50</v>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
+        <v>388</v>
+      </c>
+      <c r="K96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>151</v>
+      </c>
+      <c r="E97" t="s">
+        <v>50</v>
+      </c>
+      <c r="F97" t="s">
+        <v>50</v>
+      </c>
+      <c r="G97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="s">
+        <v>388</v>
+      </c>
+      <c r="K97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>288</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>289</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>289</v>
+      </c>
+      <c r="K98">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>291</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>289</v>
+      </c>
+      <c r="E99" t="s">
+        <v>292</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>289</v>
+      </c>
+      <c r="K99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>294</v>
+      </c>
+      <c r="B100" t="s">
+        <v>293</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" t="s">
+        <v>292</v>
+      </c>
+      <c r="F100" t="s">
+        <v>295</v>
+      </c>
+      <c r="G100" t="s">
+        <v>295</v>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="s">
+        <v>289</v>
+      </c>
+      <c r="K100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>297</v>
+      </c>
+      <c r="B101" t="s">
+        <v>296</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+      <c r="D101" t="s">
+        <v>289</v>
+      </c>
+      <c r="E101" t="s">
+        <v>292</v>
+      </c>
+      <c r="F101" t="s">
+        <v>298</v>
+      </c>
+      <c r="G101" t="s">
+        <v>298</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" t="s">
+        <v>289</v>
+      </c>
+      <c r="K101">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>300</v>
+      </c>
+      <c r="B102" t="s">
+        <v>299</v>
+      </c>
+      <c r="C102">
+        <v>3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>289</v>
+      </c>
+      <c r="E102" t="s">
+        <v>292</v>
+      </c>
+      <c r="F102" t="s">
+        <v>301</v>
+      </c>
+      <c r="G102" t="s">
+        <v>301</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="s">
+        <v>289</v>
+      </c>
+      <c r="K102">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>303</v>
+      </c>
+      <c r="B103" t="s">
+        <v>302</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="s">
+        <v>289</v>
+      </c>
+      <c r="E103" t="s">
+        <v>292</v>
+      </c>
+      <c r="F103" t="s">
+        <v>304</v>
+      </c>
+      <c r="G103" t="s">
+        <v>304</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
+        <v>289</v>
+      </c>
+      <c r="K103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>306</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>289</v>
+      </c>
+      <c r="E104" t="s">
+        <v>307</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>289</v>
+      </c>
+      <c r="K104">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>309</v>
+      </c>
+      <c r="B105" t="s">
+        <v>308</v>
+      </c>
+      <c r="C105">
+        <v>3</v>
+      </c>
+      <c r="D105" t="s">
+        <v>289</v>
+      </c>
+      <c r="E105" t="s">
+        <v>307</v>
+      </c>
+      <c r="F105" t="s">
+        <v>295</v>
+      </c>
+      <c r="G105" t="s">
+        <v>295</v>
+      </c>
+      <c r="H105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="s">
+        <v>289</v>
+      </c>
+      <c r="K105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>311</v>
+      </c>
+      <c r="B106" t="s">
+        <v>310</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="s">
+        <v>289</v>
+      </c>
+      <c r="E106" t="s">
+        <v>307</v>
+      </c>
+      <c r="F106" t="s">
+        <v>298</v>
+      </c>
+      <c r="G106" t="s">
+        <v>298</v>
+      </c>
+      <c r="H106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="s">
+        <v>289</v>
+      </c>
+      <c r="K106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>313</v>
+      </c>
+      <c r="B107" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107">
+        <v>3</v>
+      </c>
+      <c r="D107" t="s">
+        <v>289</v>
+      </c>
+      <c r="E107" t="s">
+        <v>307</v>
+      </c>
+      <c r="F107" t="s">
+        <v>301</v>
+      </c>
+      <c r="G107" t="s">
+        <v>301</v>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" t="s">
+        <v>289</v>
+      </c>
+      <c r="K107">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>315</v>
+      </c>
+      <c r="B108" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>289</v>
+      </c>
+      <c r="E108" t="s">
+        <v>307</v>
+      </c>
+      <c r="F108" t="s">
+        <v>304</v>
+      </c>
+      <c r="G108" t="s">
+        <v>304</v>
+      </c>
+      <c r="H108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" t="s">
+        <v>289</v>
+      </c>
+      <c r="K108">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
+        <v>316</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109" t="s">
+        <v>289</v>
+      </c>
+      <c r="E109" t="s">
+        <v>307</v>
+      </c>
+      <c r="F109" t="s">
+        <v>318</v>
+      </c>
+      <c r="G109" t="s">
+        <v>318</v>
+      </c>
+      <c r="H109" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" t="s">
+        <v>289</v>
+      </c>
+      <c r="K109">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>320</v>
+      </c>
+      <c r="B110" t="s">
+        <v>319</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>289</v>
+      </c>
+      <c r="E110" t="s">
+        <v>321</v>
+      </c>
+      <c r="F110" t="s">
+        <v>321</v>
+      </c>
+      <c r="G110" t="s">
+        <v>321</v>
+      </c>
+      <c r="H110" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
+        <v>289</v>
+      </c>
+      <c r="K110">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>323</v>
+      </c>
+      <c r="B111" t="s">
+        <v>322</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>289</v>
+      </c>
+      <c r="E111" t="s">
+        <v>324</v>
+      </c>
+      <c r="F111" t="s">
+        <v>324</v>
+      </c>
+      <c r="G111" t="s">
+        <v>324</v>
+      </c>
+      <c r="H111" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
+        <v>289</v>
+      </c>
+      <c r="K111">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>326</v>
+      </c>
+      <c r="B112" t="s">
+        <v>325</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
+        <v>289</v>
+      </c>
+      <c r="E112" t="s">
+        <v>327</v>
+      </c>
+      <c r="F112" t="s">
+        <v>327</v>
+      </c>
+      <c r="G112" t="s">
+        <v>327</v>
+      </c>
+      <c r="H112" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>289</v>
+      </c>
+      <c r="K112">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>329</v>
+      </c>
+      <c r="B113" t="s">
+        <v>328</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>289</v>
+      </c>
+      <c r="E113" t="s">
+        <v>330</v>
+      </c>
+      <c r="F113" t="s">
+        <v>330</v>
+      </c>
+      <c r="G113" t="s">
+        <v>330</v>
+      </c>
+      <c r="H113" t="b">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>289</v>
+      </c>
+      <c r="K113">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>332</v>
+      </c>
+      <c r="B114" t="s">
+        <v>331</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>289</v>
+      </c>
+      <c r="E114" t="s">
+        <v>333</v>
+      </c>
+      <c r="F114" t="s">
+        <v>333</v>
+      </c>
+      <c r="G114" t="s">
+        <v>333</v>
+      </c>
+      <c r="H114" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>289</v>
+      </c>
+      <c r="K114">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>335</v>
+      </c>
+      <c r="B115" t="s">
+        <v>334</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>289</v>
+      </c>
+      <c r="E115" t="s">
+        <v>336</v>
+      </c>
+      <c r="F115" t="s">
+        <v>336</v>
+      </c>
+      <c r="G115" t="s">
+        <v>336</v>
+      </c>
+      <c r="H115" t="b">
+        <v>1</v>
+      </c>
+      <c r="J115" t="s">
+        <v>289</v>
+      </c>
+      <c r="K115">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>338</v>
+      </c>
+      <c r="B116" t="s">
+        <v>337</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>289</v>
+      </c>
+      <c r="E116" t="s">
+        <v>339</v>
+      </c>
+      <c r="F116" t="s">
+        <v>339</v>
+      </c>
+      <c r="G116" t="s">
+        <v>339</v>
+      </c>
+      <c r="H116" t="b">
+        <v>1</v>
+      </c>
+      <c r="J116" t="s">
+        <v>289</v>
+      </c>
+      <c r="K116">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>341</v>
+      </c>
+      <c r="B117" t="s">
+        <v>340</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="s">
+        <v>289</v>
+      </c>
+      <c r="E117" t="s">
+        <v>50</v>
+      </c>
+      <c r="F117" t="s">
+        <v>50</v>
+      </c>
+      <c r="G117" t="s">
+        <v>50</v>
+      </c>
+      <c r="H117" t="b">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
+        <v>289</v>
+      </c>
+      <c r="K117">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>343</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>344</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="J118" t="s">
+        <v>399</v>
+      </c>
+      <c r="K118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>346</v>
+      </c>
+      <c r="B119" t="s">
+        <v>345</v>
+      </c>
+      <c r="C119">
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
+        <v>344</v>
+      </c>
+      <c r="E119" t="s">
+        <v>347</v>
+      </c>
+      <c r="F119" t="s">
+        <v>347</v>
+      </c>
+      <c r="G119" t="s">
+        <v>347</v>
+      </c>
+      <c r="H119" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
+        <v>399</v>
+      </c>
+      <c r="K119">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>349</v>
+      </c>
+      <c r="B120" t="s">
+        <v>348</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>344</v>
+      </c>
+      <c r="E120" t="s">
+        <v>350</v>
+      </c>
+      <c r="F120" t="s">
+        <v>350</v>
+      </c>
+      <c r="G120" t="s">
+        <v>350</v>
+      </c>
+      <c r="H120" t="b">
+        <v>1</v>
+      </c>
+      <c r="J120" t="s">
+        <v>399</v>
+      </c>
+      <c r="K120">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>352</v>
+      </c>
+      <c r="B121" t="s">
+        <v>351</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>344</v>
+      </c>
+      <c r="E121" t="s">
+        <v>353</v>
+      </c>
+      <c r="F121" t="s">
+        <v>353</v>
+      </c>
+      <c r="G121" t="s">
+        <v>353</v>
+      </c>
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
+        <v>399</v>
+      </c>
+      <c r="K121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>355</v>
+      </c>
+      <c r="B122" t="s">
+        <v>354</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>344</v>
+      </c>
+      <c r="E122" t="s">
+        <v>356</v>
+      </c>
+      <c r="F122" t="s">
+        <v>356</v>
+      </c>
+      <c r="G122" t="s">
+        <v>356</v>
+      </c>
+      <c r="H122" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122" t="s">
+        <v>399</v>
+      </c>
+      <c r="K122">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>358</v>
+      </c>
+      <c r="B123" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="s">
+        <v>344</v>
+      </c>
+      <c r="E123" t="s">
+        <v>359</v>
+      </c>
+      <c r="F123" t="s">
+        <v>359</v>
+      </c>
+      <c r="G123" t="s">
+        <v>359</v>
+      </c>
+      <c r="H123" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>399</v>
+      </c>
+      <c r="K123">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>361</v>
+      </c>
+      <c r="B124" t="s">
+        <v>360</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>344</v>
+      </c>
+      <c r="E124" t="s">
+        <v>362</v>
+      </c>
+      <c r="F124" t="s">
+        <v>362</v>
+      </c>
+      <c r="G124" t="s">
+        <v>362</v>
+      </c>
+      <c r="H124" t="b">
+        <v>1</v>
+      </c>
+      <c r="J124" t="s">
+        <v>399</v>
+      </c>
+      <c r="K124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>364</v>
+      </c>
+      <c r="B125" t="s">
+        <v>363</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+      <c r="D125" t="s">
+        <v>344</v>
+      </c>
+      <c r="E125" t="s">
+        <v>365</v>
+      </c>
+      <c r="F125" t="s">
+        <v>365</v>
+      </c>
+      <c r="G125" t="s">
+        <v>365</v>
+      </c>
+      <c r="H125" t="b">
+        <v>1</v>
+      </c>
+      <c r="J125" t="s">
+        <v>399</v>
+      </c>
+      <c r="K125">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>367</v>
+      </c>
+      <c r="B126" t="s">
+        <v>366</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>344</v>
+      </c>
+      <c r="E126" t="s">
+        <v>50</v>
+      </c>
+      <c r="F126" t="s">
+        <v>50</v>
+      </c>
+      <c r="G126" t="s">
+        <v>50</v>
+      </c>
+      <c r="H126" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126" t="s">
+        <v>399</v>
+      </c>
+      <c r="K126">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>396</v>
+      </c>
+      <c r="B127" t="s">
+        <v>397</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+      <c r="D127" t="s">
+        <v>344</v>
+      </c>
+      <c r="E127" t="s">
+        <v>398</v>
+      </c>
+      <c r="F127" t="s">
+        <v>398</v>
+      </c>
+      <c r="G127" t="s">
+        <v>398</v>
+      </c>
+      <c r="H127" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" t="s">
+        <v>399</v>
+      </c>
+      <c r="K127">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>369</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="s">
+        <v>370</v>
+      </c>
+      <c r="H128" t="b">
+        <v>0</v>
+      </c>
+      <c r="J128" t="s">
+        <v>370</v>
+      </c>
+      <c r="K128">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>372</v>
+      </c>
+      <c r="B129" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>370</v>
+      </c>
+      <c r="E129" t="s">
+        <v>373</v>
+      </c>
+      <c r="F129" t="s">
+        <v>373</v>
+      </c>
+      <c r="G129" t="s">
+        <v>373</v>
+      </c>
+      <c r="H129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" t="s">
+        <v>370</v>
+      </c>
+      <c r="K129">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>375</v>
+      </c>
+      <c r="B130" t="s">
+        <v>374</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+      <c r="D130" t="s">
+        <v>370</v>
+      </c>
+      <c r="E130" t="s">
+        <v>376</v>
+      </c>
+      <c r="F130" t="s">
+        <v>376</v>
+      </c>
+      <c r="G130" t="s">
+        <v>376</v>
+      </c>
+      <c r="H130" t="b">
+        <v>1</v>
+      </c>
+      <c r="J130" t="s">
+        <v>370</v>
+      </c>
+      <c r="K130">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>378</v>
+      </c>
+      <c r="B131" t="s">
+        <v>377</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+      <c r="D131" t="s">
+        <v>370</v>
+      </c>
+      <c r="E131" t="s">
+        <v>379</v>
+      </c>
+      <c r="F131" t="s">
+        <v>379</v>
+      </c>
+      <c r="G131" t="s">
+        <v>379</v>
+      </c>
+      <c r="H131" t="b">
+        <v>1</v>
+      </c>
+      <c r="J131" t="s">
+        <v>370</v>
+      </c>
+      <c r="K131">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>381</v>
+      </c>
+      <c r="B132" t="s">
+        <v>380</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132" t="s">
+        <v>370</v>
+      </c>
+      <c r="E132" t="s">
+        <v>382</v>
+      </c>
+      <c r="F132" t="s">
+        <v>382</v>
+      </c>
+      <c r="G132" t="s">
+        <v>382</v>
+      </c>
+      <c r="H132" t="b">
+        <v>1</v>
+      </c>
+      <c r="J132" t="s">
+        <v>370</v>
+      </c>
+      <c r="K132">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>384</v>
+      </c>
+      <c r="B133" t="s">
+        <v>383</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133" t="s">
+        <v>370</v>
+      </c>
+      <c r="E133" t="s">
+        <v>50</v>
+      </c>
+      <c r="F133" t="s">
+        <v>50</v>
+      </c>
+      <c r="G133" t="s">
+        <v>50</v>
+      </c>
+      <c r="H133" t="b">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
+        <v>370</v>
+      </c>
+      <c r="K133">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>386</v>
+      </c>
+      <c r="B134" t="s">
+        <v>385</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="D134" t="s">
+        <v>370</v>
+      </c>
+      <c r="E134" t="s">
+        <v>124</v>
+      </c>
+      <c r="F134" t="s">
+        <v>124</v>
+      </c>
+      <c r="G134" t="s">
+        <v>124</v>
+      </c>
+      <c r="H134" t="b">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
+        <v>370</v>
+      </c>
+      <c r="K134">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>390</v>
+      </c>
+      <c r="B135" t="s">
+        <v>389</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>50</v>
+      </c>
+      <c r="E135" t="s">
+        <v>50</v>
+      </c>
+      <c r="F135" t="s">
+        <v>50</v>
+      </c>
+      <c r="G135" t="s">
+        <v>50</v>
+      </c>
+      <c r="H135" t="b">
+        <v>1</v>
+      </c>
+      <c r="J135" t="s">
+        <v>370</v>
+      </c>
+      <c r="K135">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>